--- a/Excel/MetalConfig.xlsx
+++ b/Excel/MetalConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>

--- a/Excel/MetalConfig.xlsx
+++ b/Excel/MetalConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
   <si>
     <t>Id</t>
   </si>
@@ -44,24 +44,24 @@
     <t>RiseAttr</t>
   </si>
   <si>
+    <t>RisePower</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>RiseQuality</t>
+  </si>
+  <si>
+    <t>Des</t>
+  </si>
+  <si>
     <t>RiseLog</t>
   </si>
   <si>
-    <t>RisePower</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>RiseQuality</t>
-  </si>
-  <si>
-    <t>Des</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -222,6 +222,36 @@
   </si>
   <si>
     <t>减伤</t>
+  </si>
+  <si>
+    <t>物伤石</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤石</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤石</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>韧性石</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>破韧石</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
   </si>
   <si>
     <t>矿石之精</t>
@@ -1210,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M35"/>
+  <dimension ref="C3:M45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1237,23 +1267,23 @@
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1273,22 +1303,22 @@
         <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -2238,13 +2268,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:13">
       <c r="C32" s="1">
-        <v>101</v>
-      </c>
-      <c r="D32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>2007</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -2259,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>66</v>
@@ -2273,13 +2303,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:13">
       <c r="C33" s="1">
-        <v>102</v>
-      </c>
-      <c r="D33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E33" s="1">
-        <v>0</v>
+        <v>2008</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -2294,13 +2324,13 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>68</v>
@@ -2308,13 +2338,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:13">
       <c r="C34" s="1">
-        <v>103</v>
-      </c>
-      <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E34" s="1">
-        <v>0</v>
+        <v>2009</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -2329,13 +2359,13 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>70</v>
@@ -2343,13 +2373,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:13">
       <c r="C35" s="1">
-        <v>104</v>
-      </c>
-      <c r="D35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E35" s="1">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
@@ -2364,16 +2394,206 @@
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L35" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2013</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>100</v>
+      </c>
+      <c r="K36" s="1">
+        <v>6</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
+        <v>101</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>7</v>
+      </c>
+      <c r="L42" s="1">
+        <v>3</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>102</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>7</v>
+      </c>
+      <c r="L43" s="1">
+        <v>4</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
+        <v>103</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>7</v>
+      </c>
+      <c r="L44" s="1">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
+        <v>104</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>7</v>
+      </c>
+      <c r="L45" s="1">
+        <v>6</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MetalConfig.xlsx
+++ b/Excel/MetalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Id</t>
   </si>
@@ -44,12 +44,12 @@
     <t>RiseAttr</t>
   </si>
   <si>
+    <t>RiseLog</t>
+  </si>
+  <si>
     <t>RisePower</t>
   </si>
   <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -59,9 +59,6 @@
     <t>Des</t>
   </si>
   <si>
-    <t>RiseLog</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -252,6 +249,45 @@
   </si>
   <si>
     <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>极·墨水晶</t>
+  </si>
+  <si>
+    <t>极·蓝水晶</t>
+  </si>
+  <si>
+    <t>极·方解石</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>极·橄榄石</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>极·星叶石</t>
+  </si>
+  <si>
+    <t>极·韧性石</t>
+  </si>
+  <si>
+    <t>极·物伤石</t>
+  </si>
+  <si>
+    <t>极·法伤石</t>
+  </si>
+  <si>
+    <t>极·道伤石</t>
+  </si>
+  <si>
+    <t>极·黑曜石</t>
+  </si>
+  <si>
+    <t>极·破韧石</t>
   </si>
   <si>
     <t>矿石之精</t>
@@ -1240,18 +1276,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M45"/>
+  <dimension ref="C3:L55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="11.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="10" max="11" width="11.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="26.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1267,26 +1303,23 @@
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2">
-        <v>80</v>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1303,65 +1336,59 @@
         <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1379,24 +1406,21 @@
         <v>2</v>
       </c>
       <c r="J6" s="1">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -1414,59 +1438,53 @@
         <v>2</v>
       </c>
       <c r="J7" s="1">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>3</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="K8" s="1">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -1484,24 +1502,21 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
@@ -1519,24 +1534,21 @@
         <v>2</v>
       </c>
       <c r="J10" s="1">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1">
-        <v>3</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>15</v>
@@ -1554,24 +1566,21 @@
         <v>2</v>
       </c>
       <c r="J11" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K11" s="1">
-        <v>4</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>16</v>
@@ -1589,24 +1598,21 @@
         <v>2</v>
       </c>
       <c r="J12" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>4</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>14</v>
@@ -1624,24 +1630,21 @@
         <v>2</v>
       </c>
       <c r="J13" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>4</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1">
         <v>26</v>
@@ -1659,24 +1662,21 @@
         <v>2</v>
       </c>
       <c r="J14" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K14" s="1">
-        <v>4</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>27</v>
@@ -1694,24 +1694,21 @@
         <v>2</v>
       </c>
       <c r="J15" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>4</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1">
         <v>28</v>
@@ -1729,24 +1726,21 @@
         <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>4</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1">
         <v>33</v>
@@ -1764,24 +1758,21 @@
         <v>2</v>
       </c>
       <c r="J17" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
-        <v>5</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="1">
         <v>34</v>
@@ -1799,24 +1790,21 @@
         <v>2</v>
       </c>
       <c r="J18" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>5</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:12">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="1">
         <v>35</v>
@@ -1834,24 +1822,21 @@
         <v>2</v>
       </c>
       <c r="J19" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
-        <v>5</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1">
         <v>2003</v>
@@ -1869,24 +1854,21 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1">
-        <v>6</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1">
         <v>2002</v>
@@ -1904,24 +1886,21 @@
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1">
-        <v>6</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1">
         <v>2001</v>
@@ -1939,24 +1918,21 @@
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K22" s="1">
-        <v>6</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1">
         <v>2005</v>
@@ -1974,24 +1950,21 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1">
-        <v>6</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1">
         <v>2006</v>
@@ -2009,24 +1982,21 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K24" s="1">
-        <v>6</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1">
         <v>2004</v>
@@ -2044,24 +2014,21 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K25" s="1">
-        <v>6</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" s="1">
         <v>2010</v>
@@ -2079,24 +2046,21 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K26" s="1">
-        <v>6</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" s="1">
         <v>2011</v>
@@ -2114,24 +2078,21 @@
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1">
-        <v>6</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:12">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" s="1">
         <v>7</v>
@@ -2149,24 +2110,21 @@
         <v>2</v>
       </c>
       <c r="J28" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K28" s="1">
-        <v>5</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="1">
         <v>12</v>
@@ -2184,24 +2142,21 @@
         <v>2</v>
       </c>
       <c r="J29" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1">
-        <v>5</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="1">
         <v>9</v>
@@ -2219,24 +2174,21 @@
         <v>2</v>
       </c>
       <c r="J30" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K30" s="1">
-        <v>5</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" s="1">
         <v>13</v>
@@ -2254,24 +2206,21 @@
         <v>2</v>
       </c>
       <c r="J31" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1">
-        <v>5</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" s="1">
         <v>2007</v>
@@ -2289,24 +2238,21 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1">
-        <v>6</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" s="1">
         <v>2008</v>
@@ -2324,24 +2270,21 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K33" s="1">
-        <v>6</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1">
         <v>2009</v>
@@ -2359,24 +2302,21 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1">
-        <v>6</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:12">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35" s="1">
         <v>2012</v>
@@ -2394,24 +2334,21 @@
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1">
-        <v>6</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:12">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1">
         <v>2013</v>
@@ -2429,171 +2366,505 @@
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2003</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>7</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2001</v>
+      </c>
+      <c r="F38" s="1">
+        <v>2</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>7</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>7</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F40" s="1">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>7</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>7</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>7</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:12">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>7</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:12">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F44" s="1">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>7</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:12">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>7</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:12">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2010</v>
+      </c>
+      <c r="F46" s="1">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>7</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:12">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2013</v>
+      </c>
+      <c r="F47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>7</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:12">
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:12">
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:12">
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:12">
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:12">
+      <c r="C52" s="1">
+        <v>101</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>7</v>
+      </c>
+      <c r="K52" s="1">
+        <v>3</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:12">
+      <c r="C53" s="1">
+        <v>102</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>7</v>
+      </c>
+      <c r="K53" s="1">
+        <v>4</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:12">
+      <c r="C54" s="1">
+        <v>103</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>7</v>
+      </c>
+      <c r="K54" s="1">
+        <v>5</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:12">
+      <c r="C55" s="1">
+        <v>104</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>7</v>
+      </c>
+      <c r="K55" s="1">
         <v>6</v>
       </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
-        <v>101</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <v>7</v>
-      </c>
-      <c r="L42" s="1">
-        <v>3</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
-        <v>102</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
-        <v>0</v>
-      </c>
-      <c r="K43" s="1">
-        <v>7</v>
-      </c>
-      <c r="L43" s="1">
-        <v>4</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
-        <v>103</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="1">
-        <v>0</v>
-      </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>7</v>
-      </c>
-      <c r="L44" s="1">
-        <v>5</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
-        <v>104</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E45" s="1">
-        <v>0</v>
-      </c>
-      <c r="F45" s="1">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1">
-        <v>7</v>
-      </c>
-      <c r="L45" s="1">
-        <v>6</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>82</v>
+      <c r="L55" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
